--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0110.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0110.xlsx
@@ -21022,7 +21022,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Pioneer Podcast Weapon Chest</t>
+          <t>Pioneer Podcast Vũ khí Chest</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Rangers' Series Weapon Supply Chest</t>
+          <t>Rangers' Series Vũ khí Supply Chest</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22212,7 +22212,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Deep Sky Blazar Weapon Chest</t>
+          <t>Deep Sky Blazar Vũ khí Chest</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22562,7 +22562,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Originite Weapon Supply Chest</t>
+          <t>Originite Vũ khí Supply Chest</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Exiles' Weapon</t>
+          <t>Exiles' Vũ khí</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
